--- a/data/import_template.xlsx
+++ b/data/import_template.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="跌倒风险评估表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fall Risk Assessment" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,140 +423,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>姓名</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>性别</t>
+          <t>age</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>年龄</t>
+          <t>night_bed_exits</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>夜间离床次数</t>
+          <t>night_activity_duration_min</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>夜间活动时长(分钟)</t>
+          <t>past_falls</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>过去跌倒次数</t>
+          <t>mobility_score</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>活动能力评分</t>
+          <t>high_risk_medication</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>是否使用高风险药物</t>
+          <t>cognitive_impairment</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>认知障碍程度</t>
+          <t>polypharmacy_count</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>多重用药数量</t>
+          <t>orthostatic_hypotension</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>是否有体位性低血压</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>起立行走测试(秒)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>示例-请删除此行</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>82</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>18.5</v>
+          <t>tug_seconds</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"男,女"</formula1>
+    <dataValidation sqref="A2:A2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Male,Female"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H2000 K2:K2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"是,否"</formula1>
+    <dataValidation sqref="G2:G2000 J2:J2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/import_template.xlsx
+++ b/data/import_template.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,6 +437,9 @@
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,6 +496,21 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tug_seconds</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>days_since_last_fall</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>syncopal_fall</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>fall_cluster_30d</t>
         </is>
       </c>
     </row>
@@ -501,7 +519,7 @@
     <dataValidation sqref="A2:A2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Male,Female"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2000 J2:J2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G2000 J2:J2000 M2:M2000 N2:N2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
